--- a/Sand Project/mine_locs_2024.xlsx
+++ b/Sand Project/mine_locs_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jleedy\Documents\Coursework\SP26\Data Science\solar-incentive-adoption\Sand Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A919073E-54E8-4CEA-BBBB-0B393DB415E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553D60BE-05B5-4A3A-A10E-380E6A144281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="270">
   <si>
     <t xml:space="preserve"> 59 Federal Road Map 131 Lot 1-1 + 131-1-2 </t>
   </si>
@@ -739,33 +739,18 @@
     <t>Squirrel Island Road</t>
   </si>
   <si>
-    <t>Commerce Park/0 Colony Place  Lot 26</t>
-  </si>
-  <si>
     <t>Colony Place Development LLC</t>
   </si>
   <si>
     <t>Business Park</t>
   </si>
   <si>
-    <t>Commerce Park/ 0 Colony Place Lot 29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commerce Park/Colony Place Map 102/Lot 26-2 </t>
-  </si>
-  <si>
     <t>Gary Darmin</t>
   </si>
   <si>
-    <t xml:space="preserve">Commerce Park Colony Place Map 105, Lot 27 </t>
-  </si>
-  <si>
     <t>Commerce Park LLC</t>
   </si>
   <si>
-    <t xml:space="preserve">Commerce Park Colony Place Map 104 Lot 14  </t>
-  </si>
-  <si>
     <t>Dundee Corp.</t>
   </si>
   <si>
@@ -782,9 +767,6 @@
   </si>
   <si>
     <t>Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 360 Cherry Street</t>
   </si>
   <si>
     <t>T.L. Edwards Inc.</t>
@@ -1241,6 +1223,15 @@
   </si>
   <si>
     <t>Park Avenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 360 Cherry Street, Plymouth, MA</t>
+  </si>
+  <si>
+    <t>Commerce Park Colony Place</t>
   </si>
 </sst>
 </file>
@@ -1854,40 +1845,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2081,7 +2072,7 @@
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>1</v>
@@ -2644,7 +2635,7 @@
         <v>52</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C24" s="15">
         <v>50000</v>
@@ -2682,7 +2673,7 @@
         <v>53</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C25" s="15">
         <v>2250000</v>
@@ -2718,7 +2709,7 @@
         <v>54</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C26" s="15">
         <v>60000</v>
@@ -2754,7 +2745,7 @@
         <v>55</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C27" s="15">
         <v>350000</v>
@@ -3033,7 +3024,7 @@
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>71</v>
@@ -3191,7 +3182,7 @@
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>80</v>
@@ -3237,10 +3228,10 @@
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C43" s="33">
         <v>52600</v>
@@ -3265,7 +3256,7 @@
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>83</v>
@@ -3289,7 +3280,7 @@
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>84</v>
@@ -3411,7 +3402,7 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>1</v>
@@ -3863,10 +3854,10 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="39" t="s">
         <v>121</v>
-      </c>
-      <c r="B65" s="39" t="s">
-        <v>122</v>
       </c>
       <c r="C65" s="12">
         <v>340204</v>
@@ -3875,7 +3866,7 @@
         <v>14</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>4</v>
@@ -3891,10 +3882,10 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66" s="12">
         <v>174705</v>
@@ -3903,7 +3894,7 @@
         <v>12</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F66" s="35" t="s">
         <v>4</v>
@@ -3918,11 +3909,11 @@
       <c r="L66" s="13"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="40" t="s">
-        <v>125</v>
+      <c r="A67" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C67" s="31">
         <v>2500000</v>
@@ -3931,7 +3922,7 @@
         <v>106</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>4</v>
@@ -3948,18 +3939,18 @@
       <c r="L67" s="13"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="40" t="s">
-        <v>127</v>
+      <c r="A68" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C68" s="30">
         <v>1000000</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>4</v>
@@ -3976,11 +3967,11 @@
       <c r="L68" s="13"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="40" t="s">
-        <v>129</v>
+      <c r="A69" s="16" t="s">
+        <v>269</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C69" s="29">
         <v>139929</v>
@@ -3989,7 +3980,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>4</v>
@@ -4007,17 +3998,17 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="40" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C70" s="30">
         <v>250000</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>4</v>
@@ -4035,10 +4026,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C71" s="12">
         <v>2821906</v>
@@ -4047,7 +4038,7 @@
         <v>50</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F71" s="19" t="s">
         <v>4</v>
@@ -4061,17 +4052,17 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="12">
         <v>35</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>4</v>
@@ -4087,10 +4078,10 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B73" s="41" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C73" s="12">
         <v>571838</v>
@@ -4099,7 +4090,7 @@
         <v>14</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>4</v>
@@ -4117,10 +4108,10 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="16" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C74" s="12">
         <v>4285981</v>
@@ -4149,10 +4140,10 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="16" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C75" s="12">
         <v>705672</v>
@@ -4177,10 +4168,10 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="16" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C76" s="12">
         <v>121807</v>
@@ -4189,7 +4180,7 @@
         <v>5</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F76" s="13" t="s">
         <v>4</v>
@@ -4207,10 +4198,10 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="16" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B77" s="39" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C77" s="12">
         <v>621133</v>
@@ -4219,10 +4210,10 @@
         <v>22</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G77" s="13"/>
       <c r="H77" s="13" t="s">
@@ -4234,15 +4225,15 @@
         <v>4</v>
       </c>
       <c r="L77" s="13" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C78" s="12">
         <v>267813</v>
@@ -4251,7 +4242,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F78" s="13" t="s">
         <v>3</v>
@@ -4269,10 +4260,10 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C79" s="15">
         <v>896000</v>
@@ -4281,7 +4272,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>3</v>
@@ -4299,10 +4290,10 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C80" s="12">
         <v>60000</v>
@@ -4325,10 +4316,10 @@
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C81" s="15">
         <v>998871</v>
@@ -4337,10 +4328,10 @@
         <v>20</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G81" s="13"/>
       <c r="H81" s="13" t="s">
@@ -4359,10 +4350,10 @@
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C82" s="12">
         <v>993168</v>
@@ -4371,7 +4362,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F82" s="13" t="s">
         <v>95</v>
@@ -4391,10 +4382,10 @@
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="16" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C83" s="12">
         <v>615809</v>
@@ -4403,7 +4394,7 @@
         <v>19</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>95</v>
@@ -4425,10 +4416,10 @@
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="16" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C84" s="15">
         <v>112288</v>
@@ -4453,17 +4444,17 @@
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="16" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B85" s="39" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
         <v>112</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F85" s="13" t="s">
         <v>4</v>
@@ -4481,17 +4472,17 @@
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B86" s="39" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C86" s="12"/>
       <c r="D86" s="12">
         <v>0</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F86" s="13" t="s">
         <v>4</v>
@@ -4509,17 +4500,17 @@
     </row>
     <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="16" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C87" s="12"/>
       <c r="D87" s="12">
         <v>0</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F87" s="13" t="s">
         <v>4</v>
@@ -4537,10 +4528,10 @@
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="16" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C88" s="43">
         <v>396396</v>
@@ -4549,7 +4540,7 @@
         <v>39</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F88" s="13" t="s">
         <v>4</v>
@@ -4569,15 +4560,15 @@
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="16" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B89" s="39" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F89" s="13" t="s">
         <v>4</v>
@@ -4591,10 +4582,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C90" s="12">
         <v>550000</v>
@@ -4603,7 +4594,7 @@
         <v>7</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F90" s="13" t="s">
         <v>4</v>
@@ -4625,10 +4616,10 @@
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B91" s="39" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C91" s="12">
         <v>23877</v>
@@ -4637,7 +4628,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F91" s="13" t="s">
         <v>4</v>
@@ -4653,10 +4644,10 @@
     </row>
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B92" s="39" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C92" s="12"/>
       <c r="D92" s="12" t="e">
@@ -4664,7 +4655,7 @@
         <v>#REF!</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F92" s="13" t="s">
         <v>4</v>
@@ -4678,13 +4669,13 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="21" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B93" s="39"/>
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="13" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>4</v>
@@ -4698,17 +4689,17 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="16" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B94" s="39" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C94" s="15">
         <v>550000</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F94" s="13" t="s">
         <v>4</v>
@@ -4722,10 +4713,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="16" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C95" s="12">
         <v>282656</v>
@@ -4734,7 +4725,7 @@
         <v>12</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>4</v>
@@ -4752,10 +4743,10 @@
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B96" s="39" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C96" s="12">
         <v>1259965</v>
@@ -4764,7 +4755,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F96" s="13"/>
       <c r="G96" s="13"/>
@@ -4776,10 +4767,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="16" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B97" s="39" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C97" s="12">
         <v>817999</v>
@@ -4808,10 +4799,10 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="44" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B98" s="39" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C98" s="45">
         <v>850000</v>
@@ -4820,7 +4811,7 @@
         <v>22</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F98" s="13" t="s">
         <v>3</v>
@@ -4838,10 +4829,10 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="21" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B99" s="39" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C99" s="12">
         <v>445964</v>
@@ -4850,7 +4841,7 @@
         <v>6</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F99" s="13" t="s">
         <v>4</v>
@@ -4870,10 +4861,10 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="21" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C100" s="12">
         <v>871045</v>
@@ -4885,11 +4876,11 @@
         <v>23</v>
       </c>
       <c r="F100" s="46" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G100" s="13"/>
       <c r="H100" s="13" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I100" s="13" t="s">
         <v>3</v>
@@ -4902,10 +4893,10 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="21" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C101" s="47"/>
       <c r="D101" s="13">
@@ -4932,17 +4923,17 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C102" s="47"/>
       <c r="D102" s="13">
         <v>42</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F102" s="13" t="s">
         <v>4</v>
@@ -4962,17 +4953,17 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="16" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C103" s="47"/>
       <c r="D103" s="13">
         <v>136</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F103" s="13" t="s">
         <v>4</v>
@@ -4998,10 +4989,10 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="16" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B104" s="39" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C104" s="47">
         <v>175000</v>
@@ -5010,7 +5001,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F104" s="13" t="s">
         <v>4</v>
@@ -5032,7 +5023,7 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="16" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B105" s="39"/>
       <c r="C105" s="47">
@@ -5042,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F105" s="13"/>
       <c r="G105" s="13" t="s">
@@ -5062,19 +5053,19 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="21" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B106" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="C106" s="47">
-        <v>300000</v>
+        <v>216</v>
+      </c>
+      <c r="C106" s="47" t="s">
+        <v>267</v>
       </c>
       <c r="D106" s="13">
         <v>78</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F106" s="13"/>
       <c r="G106" s="13"/>
@@ -5092,23 +5083,23 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="21" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B107" s="39" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C107" s="13"/>
       <c r="D107" s="13">
         <v>72</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F107" s="13" t="s">
         <v>4</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H107" s="13" t="s">
         <v>3</v>
@@ -5124,10 +5115,10 @@
     </row>
     <row r="108" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="49" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B108" s="39" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C108" s="13">
         <v>372680</v>
@@ -5152,10 +5143,10 @@
     </row>
     <row r="109" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="49" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C109" s="47">
         <v>167000</v>
@@ -5164,10 +5155,10 @@
         <v>15</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G109" s="13" t="s">
         <v>3</v>
@@ -5188,10 +5179,10 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C110" s="47">
         <v>69129</v>
@@ -5220,7 +5211,7 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="51" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>1</v>
@@ -5248,10 +5239,10 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="51" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C112" s="50">
         <v>1000000</v>
@@ -5271,15 +5262,15 @@
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
       <c r="L112" s="50" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="51" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B113" s="39" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C113" s="50">
         <v>475000</v>
@@ -5288,7 +5279,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F113" s="50"/>
       <c r="G113" s="50" t="s">
@@ -5301,15 +5292,15 @@
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
       <c r="L113" s="50" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="51" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C114" s="50">
         <v>1140000</v>
@@ -5327,12 +5318,12 @@
       <c r="J114" s="50"/>
       <c r="K114" s="50"/>
       <c r="L114" s="50" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="49" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B115" s="52" t="s">
         <v>1</v>
@@ -5344,7 +5335,7 @@
         <v>15</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F115" s="50"/>
       <c r="G115" s="50"/>
@@ -5358,10 +5349,10 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="49" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B116" s="54" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C116" s="53">
         <v>1530000</v>
@@ -5370,7 +5361,7 @@
         <v>20</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F116" s="50"/>
       <c r="G116" s="50"/>
@@ -5387,7 +5378,7 @@
         <v>3</v>
       </c>
       <c r="L116" s="50" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/Sand Project/mine_locs_2024.xlsx
+++ b/Sand Project/mine_locs_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jleedy\Documents\Coursework\SP26\Data Science\solar-incentive-adoption\Sand Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553D60BE-05B5-4A3A-A10E-380E6A144281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C70B5A-2C45-4485-A34F-CA29AB3AEC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Earth Removal" sheetId="1" r:id="rId1"/>
@@ -239,9 +239,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="270">
   <si>
-    <t xml:space="preserve"> 59 Federal Road Map 131 Lot 1-1 + 131-1-2 </t>
-  </si>
-  <si>
     <t>AD Makepeace Cranberry</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
     <t>MEPA TMUD Area</t>
   </si>
   <si>
-    <t xml:space="preserve"> 46 Federal Rd. Map 131-2-4 (Numerous Permits)</t>
-  </si>
-  <si>
     <t>Cranberry bog/pond</t>
   </si>
   <si>
@@ -272,74 +266,13 @@
     <t>Planned Per ISO</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>24</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF0563C1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> Hammond Street Map 134-4-2A (Permi</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF0563C1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>t 2019)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Cranberry bog/pond </t>
   </si>
   <si>
     <t>No review</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF0563C1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF0563C1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Hammond Street: 131 lot 1-3 </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>(Solar)</t>
-    </r>
-  </si>
-  <si>
     <t>Solar</t>
-  </si>
-  <si>
-    <t>276 Federal Road Map 131-2-A (Solar/Mining)</t>
   </si>
   <si>
     <t>ESA Permit</t>
@@ -1180,9 +1113,6 @@
     <t>MEPA_form</t>
   </si>
   <si>
-    <t xml:space="preserve"> Finney Bogs, Sppit Road-0 Pond St. (Permit)</t>
-  </si>
-  <si>
     <t>Federal Furce Cranberry</t>
   </si>
   <si>
@@ -1232,6 +1162,41 @@
   </si>
   <si>
     <t>Commerce Park Colony Place</t>
+  </si>
+  <si>
+    <t>0 Hammond Street</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF0563C1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Hammond Street</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> 46 Federal Rd. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 59 Federal Road </t>
+  </si>
+  <si>
+    <t>276 Federal Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finney Bogs, Sppit Road-0 Pond St.</t>
   </si>
 </sst>
 </file>
@@ -1845,48 +1810,48 @@
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>1</v>
       </c>
       <c r="C2" s="11">
         <v>6652425</v>
@@ -1895,36 +1860,36 @@
         <v>105</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="13" t="s">
+      <c r="K2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>7</v>
+        <v>266</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="11">
         <v>3691493</v>
@@ -1933,36 +1898,36 @@
         <v>52</v>
       </c>
       <c r="E3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>10</v>
-      </c>
       <c r="L3" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="15">
         <v>581000</v>
@@ -1971,34 +1936,34 @@
         <v>41</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="12">
         <v>1158566</v>
@@ -2007,36 +1972,36 @@
         <v>25</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="11">
         <f>488769/5</f>
@@ -2046,36 +2011,36 @@
         <v>85</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="13" t="s">
+      <c r="J6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="11">
         <f t="shared" ref="C7:C10" si="0">488769/5</f>
@@ -2083,34 +2048,34 @@
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
@@ -2118,34 +2083,34 @@
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11">
         <f t="shared" si="0"/>
@@ -2155,34 +2120,34 @@
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="11">
         <f t="shared" si="0"/>
@@ -2192,26 +2157,26 @@
         <v>15</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="15">
         <v>1716000</v>
@@ -2228,10 +2193,10 @@
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="15">
         <v>1687990</v>
@@ -2242,22 +2207,22 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K12" s="13"/>
       <c r="L12" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C13" s="12">
         <v>2494913</v>
@@ -2266,36 +2231,36 @@
         <v>18</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" s="15">
         <v>120000</v>
@@ -2304,36 +2269,36 @@
         <v>6</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="12">
         <v>451591</v>
@@ -2342,32 +2307,32 @@
         <v>22</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C16" s="12">
         <v>568666</v>
@@ -2376,32 +2341,32 @@
         <v>10</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C17" s="12">
         <v>22049</v>
@@ -2410,34 +2375,34 @@
         <v>3</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C18" s="15">
         <v>450000</v>
@@ -2446,32 +2411,32 @@
         <v>27</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K18" s="13"/>
       <c r="L18" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C19" s="12">
         <v>75393</v>
@@ -2480,60 +2445,60 @@
         <v>4</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18">
         <v>25</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C21" s="15">
         <v>62000</v>
@@ -2542,30 +2507,30 @@
         <v>11</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K21" s="13"/>
       <c r="L21" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C22" s="15">
         <v>40000</v>
@@ -2574,34 +2539,34 @@
         <v>6</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K22" s="13"/>
       <c r="L22" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C23" s="12">
         <v>334231</v>
@@ -2610,32 +2575,32 @@
         <v>10</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K23" s="13"/>
       <c r="L23" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C24" s="15">
         <v>50000</v>
@@ -2644,144 +2609,144 @@
         <v>102</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C25" s="15">
         <v>2250000</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C26" s="15">
         <v>60000</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C27" s="15">
         <v>350000</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L27" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C28" s="12">
         <v>647837</v>
@@ -2790,88 +2755,88 @@
         <v>50</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="18"/>
       <c r="B29" s="10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C29" s="15">
         <v>400000</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
       <c r="I29" s="13"/>
       <c r="J29" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12">
         <v>22</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
       <c r="J30" s="13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C31" s="12">
         <v>557349</v>
@@ -2880,34 +2845,34 @@
         <v>22</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="26" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C32" s="18">
         <v>207485</v>
@@ -2915,60 +2880,60 @@
       <c r="D32" s="18"/>
       <c r="E32" s="18"/>
       <c r="G32" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="24"/>
       <c r="I32" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C33" s="29">
         <v>65000</v>
       </c>
       <c r="D33" s="30"/>
       <c r="E33" s="31" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F33" s="31"/>
       <c r="G33" s="31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="31"/>
       <c r="K33" s="31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" s="31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C34" s="12">
         <v>581981</v>
@@ -2977,29 +2942,29 @@
         <v>20</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="18"/>
@@ -3007,27 +2972,27 @@
         <v>12</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="24"/>
       <c r="K35" s="24"/>
       <c r="L35" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C36" s="15">
         <v>80000</v>
@@ -3037,12 +3002,12 @@
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
       <c r="I36" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
@@ -3050,142 +3015,142 @@
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C37" s="15">
         <v>150000</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
       <c r="I37" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C38" s="15">
         <v>170000</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C39" s="15">
         <v>525000</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C40" s="15">
         <v>365000</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C41" s="33">
         <v>16400</v>
@@ -3196,20 +3161,20 @@
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
       <c r="I41" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="13"/>
       <c r="L41" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="13"/>
@@ -3218,48 +3183,48 @@
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
       <c r="I42" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="13"/>
       <c r="L42" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C43" s="33">
         <v>52600</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
       <c r="I43" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="13"/>
       <c r="L43" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C44" s="33">
         <v>137470</v>
@@ -3270,26 +3235,26 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="I44" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44" s="13"/>
       <c r="K44" s="13"/>
       <c r="L44" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C45" s="33"/>
       <c r="D45" s="13"/>
       <c r="E45" s="13"/>
       <c r="F45" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
@@ -3297,13 +3262,13 @@
       <c r="J45" s="13"/>
       <c r="K45" s="13"/>
       <c r="L45" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="13"/>
@@ -3315,7 +3280,7 @@
       <c r="J46" s="13"/>
       <c r="K46" s="13"/>
       <c r="L46" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3331,15 +3296,15 @@
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
       <c r="L47" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C48" s="33">
         <v>250000</v>
@@ -3348,64 +3313,64 @@
         <v>25</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="13"/>
       <c r="H48" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="13"/>
       <c r="K48" s="13" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="24">
         <v>3</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="18"/>
       <c r="H49" s="24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" s="24"/>
       <c r="K49" s="24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="13">
         <v>3059380</v>
@@ -3414,34 +3379,34 @@
         <v>50</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="13">
         <v>320086</v>
@@ -3450,32 +3415,32 @@
         <v>37</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="12">
         <v>458883</v>
@@ -3484,32 +3449,32 @@
         <v>12</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J52" s="13"/>
       <c r="K52" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="12">
         <v>2107955</v>
@@ -3518,34 +3483,34 @@
         <v>45</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C54" s="12">
         <v>1802572</v>
@@ -3554,28 +3519,28 @@
         <v>150</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
       <c r="K54" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C55" s="12">
         <v>642252</v>
@@ -3584,28 +3549,28 @@
         <v>18</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
       <c r="K55" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="37" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C56" s="12">
         <v>685383</v>
@@ -3614,28 +3579,28 @@
         <v>36</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
       <c r="K56" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="37" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C57" s="15">
         <v>315581</v>
@@ -3645,25 +3610,25 @@
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
       <c r="K57" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C58" s="15">
         <v>117086</v>
@@ -3672,136 +3637,136 @@
         <v>8</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F58" s="38"/>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
       <c r="I58" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="13"/>
       <c r="K58" s="13"/>
       <c r="L58" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="12"/>
       <c r="E59" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
       <c r="I59" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="13"/>
       <c r="K59" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="12">
         <v>3</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
       <c r="K60" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="12"/>
       <c r="E61" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
       <c r="I61" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" s="13"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="12">
         <v>15</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
       <c r="I62" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J62" s="13"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C63" s="15">
         <v>103445</v>
@@ -3810,10 +3775,10 @@
         <v>8</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
@@ -3821,12 +3786,12 @@
       <c r="J63" s="13"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="15"/>
@@ -3834,30 +3799,30 @@
         <v>30</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C65" s="12">
         <v>340204</v>
@@ -3866,13 +3831,13 @@
         <v>14</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
@@ -3882,10 +3847,10 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C66" s="12">
         <v>174705</v>
@@ -3894,13 +3859,13 @@
         <v>12</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
@@ -3910,10 +3875,10 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C67" s="31">
         <v>2500000</v>
@@ -3922,17 +3887,17 @@
         <v>106</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" s="13"/>
       <c r="K67" s="13"/>
@@ -3940,27 +3905,27 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C68" s="30">
         <v>1000000</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J68" s="13"/>
       <c r="K68" s="13"/>
@@ -3968,10 +3933,10 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C69" s="29">
         <v>139929</v>
@@ -3980,17 +3945,17 @@
         <v>27</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J69" s="13"/>
       <c r="K69" s="13"/>
@@ -3998,27 +3963,27 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="40" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C70" s="30">
         <v>250000</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" s="13"/>
       <c r="K70" s="13"/>
@@ -4026,10 +3991,10 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C71" s="12">
         <v>2821906</v>
@@ -4038,10 +4003,10 @@
         <v>50</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
@@ -4052,23 +4017,23 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="12">
         <v>35</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -4078,10 +4043,10 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B73" s="41" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C73" s="12">
         <v>571838</v>
@@ -4090,17 +4055,17 @@
         <v>14</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" s="13"/>
       <c r="K73" s="13"/>
@@ -4108,10 +4073,10 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="16" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C74" s="12">
         <v>4285981</v>
@@ -4120,30 +4085,30 @@
         <v>85</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" s="13"/>
       <c r="I74" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J74" s="13"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="16" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C75" s="12">
         <v>705672</v>
@@ -4152,10 +4117,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
@@ -4163,15 +4128,15 @@
       <c r="J75" s="13"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B76" s="39" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C76" s="12">
         <v>121807</v>
@@ -4180,28 +4145,28 @@
         <v>5</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G76" s="13"/>
       <c r="H76" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="13"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B77" s="39" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C77" s="12">
         <v>621133</v>
@@ -4210,30 +4175,30 @@
         <v>22</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G77" s="13"/>
       <c r="H77" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="13"/>
       <c r="K77" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L77" s="13" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C78" s="12">
         <v>267813</v>
@@ -4242,28 +4207,28 @@
         <v>20</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="13"/>
       <c r="H78" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="13"/>
       <c r="K78" s="13"/>
       <c r="L78" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C79" s="15">
         <v>896000</v>
@@ -4272,38 +4237,38 @@
         <v>15</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="13"/>
       <c r="H79" s="13"/>
       <c r="I79" s="13"/>
       <c r="J79" s="13"/>
       <c r="K79" s="42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L79" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C80" s="12">
         <v>60000</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
@@ -4311,15 +4276,15 @@
       <c r="J80" s="13"/>
       <c r="K80" s="13"/>
       <c r="L80" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="16" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C81" s="15">
         <v>998871</v>
@@ -4328,32 +4293,32 @@
         <v>20</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G81" s="13"/>
       <c r="H81" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B82" s="39" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C82" s="12">
         <v>993168</v>
@@ -4362,30 +4327,30 @@
         <v>27</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G82" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H82" s="13"/>
       <c r="I82" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82" s="13"/>
       <c r="K82" s="13"/>
       <c r="L82" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C83" s="12">
         <v>615809</v>
@@ -4394,32 +4359,32 @@
         <v>19</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G83" s="13"/>
       <c r="H83" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83" s="13"/>
       <c r="K83" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L83" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="16" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C84" s="15">
         <v>112288</v>
@@ -4428,10 +4393,10 @@
         <v>12</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G84" s="13"/>
       <c r="H84" s="13"/>
@@ -4439,99 +4404,99 @@
       <c r="J84" s="13"/>
       <c r="K84" s="13"/>
       <c r="L84" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="16" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B85" s="39" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
         <v>112</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G85" s="13"/>
       <c r="H85" s="13"/>
       <c r="I85" s="13"/>
       <c r="J85" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B86" s="39" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C86" s="12"/>
       <c r="D86" s="12">
         <v>0</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" s="13"/>
       <c r="H86" s="13"/>
       <c r="I86" s="13"/>
       <c r="J86" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K86" s="13"/>
       <c r="L86" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="16" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C87" s="12"/>
       <c r="D87" s="12">
         <v>0</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G87" s="13"/>
       <c r="H87" s="13"/>
       <c r="I87" s="13"/>
       <c r="J87" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="16" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C88" s="43">
         <v>396396</v>
@@ -4540,38 +4505,38 @@
         <v>39</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
       <c r="I88" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="16" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B89" s="39" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C89" s="12"/>
       <c r="D89" s="12"/>
       <c r="E89" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
@@ -4582,10 +4547,10 @@
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C90" s="12">
         <v>550000</v>
@@ -4594,32 +4559,32 @@
         <v>7</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J90" s="13"/>
       <c r="K90" s="13"/>
       <c r="L90" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B91" s="39" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C91" s="12">
         <v>23877</v>
@@ -4628,10 +4593,10 @@
         <v>2</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F91" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
@@ -4639,15 +4604,15 @@
       <c r="J91" s="13"/>
       <c r="K91" s="13"/>
       <c r="L91" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="16" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B92" s="39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C92" s="12"/>
       <c r="D92" s="12" t="e">
@@ -4655,10 +4620,10 @@
         <v>#REF!</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
@@ -4669,16 +4634,16 @@
     </row>
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="21" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B93" s="39"/>
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="13" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
@@ -4689,20 +4654,20 @@
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B94" s="39" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C94" s="15">
         <v>550000</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G94" s="13"/>
       <c r="H94" s="13"/>
@@ -4713,10 +4678,10 @@
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="16" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C95" s="12">
         <v>282656</v>
@@ -4725,28 +4690,28 @@
         <v>12</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="13"/>
       <c r="H95" s="13"/>
       <c r="I95" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J95" s="13"/>
       <c r="K95" s="13"/>
       <c r="L95" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B96" s="39" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C96" s="12">
         <v>1259965</v>
@@ -4755,7 +4720,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F96" s="13"/>
       <c r="G96" s="13"/>
@@ -4767,10 +4732,10 @@
     </row>
     <row r="97" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B97" s="39" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C97" s="12">
         <v>817999</v>
@@ -4780,29 +4745,29 @@
       </c>
       <c r="E97" s="13"/>
       <c r="F97" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" s="13"/>
       <c r="I97" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L97" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="44" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B98" s="39" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C98" s="45">
         <v>850000</v>
@@ -4811,28 +4776,28 @@
         <v>22</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
       <c r="I98" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J98" s="13"/>
       <c r="K98" s="13"/>
       <c r="L98" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="21" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B99" s="39" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C99" s="12">
         <v>445964</v>
@@ -4841,30 +4806,30 @@
         <v>6</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F99" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H99" s="13"/>
       <c r="I99" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" s="13"/>
       <c r="K99" s="13"/>
       <c r="L99" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="21" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C100" s="12">
         <v>871045</v>
@@ -4873,126 +4838,126 @@
         <v>20</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F100" s="46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G100" s="13"/>
       <c r="H100" s="13" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J100" s="13"/>
       <c r="K100" s="13"/>
       <c r="L100" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="21" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C101" s="47"/>
       <c r="D101" s="13">
         <v>85</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" s="13"/>
       <c r="H101" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J101" s="13"/>
       <c r="K101" s="13"/>
       <c r="L101" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C102" s="47"/>
       <c r="D102" s="13">
         <v>42</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G102" s="13"/>
       <c r="H102" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J102" s="13"/>
       <c r="K102" s="13"/>
       <c r="L102" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C103" s="47"/>
       <c r="D103" s="13">
         <v>136</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F103" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L103" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B104" s="39" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C104" s="47">
         <v>175000</v>
@@ -5001,29 +4966,29 @@
         <v>10</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J104" s="13"/>
       <c r="K104" s="13"/>
       <c r="L104" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B105" s="39"/>
       <c r="C105" s="47">
@@ -5033,92 +4998,92 @@
         <v>10</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F105" s="13"/>
       <c r="G105" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J105" s="13"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="21" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B106" s="39" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D106" s="13">
         <v>78</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F106" s="13"/>
       <c r="G106" s="13"/>
       <c r="H106" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J106" s="13"/>
       <c r="K106" s="13"/>
       <c r="L106" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="21" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B107" s="39" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C107" s="13"/>
       <c r="D107" s="13">
         <v>72</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F107" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" s="13"/>
       <c r="K107" s="13"/>
       <c r="L107" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="49" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B108" s="39" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C108" s="13">
         <v>372680</v>
@@ -5129,24 +5094,24 @@
       <c r="E108" s="13"/>
       <c r="F108" s="13"/>
       <c r="G108" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="13"/>
       <c r="K108" s="13"/>
       <c r="L108" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="49" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C109" s="47">
         <v>167000</v>
@@ -5155,34 +5120,34 @@
         <v>15</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F109" s="13" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K109" s="13"/>
       <c r="L109" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="48" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C110" s="47">
         <v>69129</v>
@@ -5191,30 +5156,30 @@
         <v>12</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F110" s="13"/>
       <c r="G110" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I110" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J110" s="13"/>
       <c r="K110" s="13"/>
       <c r="L110" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="51" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" s="50">
         <v>1200000</v>
@@ -5225,24 +5190,24 @@
       <c r="E111" s="13"/>
       <c r="F111" s="50"/>
       <c r="G111" s="50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H111" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I111" s="50"/>
       <c r="J111" s="50"/>
       <c r="K111" s="50"/>
       <c r="L111" s="50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="51" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C112" s="50">
         <v>1000000</v>
@@ -5253,24 +5218,24 @@
       <c r="E112" s="13"/>
       <c r="F112" s="50"/>
       <c r="G112" s="50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H112" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I112" s="50"/>
       <c r="J112" s="50"/>
       <c r="K112" s="50"/>
       <c r="L112" s="50" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="51" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B113" s="39" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C113" s="50">
         <v>475000</v>
@@ -5279,28 +5244,28 @@
         <v>30</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F113" s="50"/>
       <c r="G113" s="50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H113" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I113" s="50"/>
       <c r="J113" s="50"/>
       <c r="K113" s="50"/>
       <c r="L113" s="50" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="51" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C114" s="50">
         <v>1140000</v>
@@ -5309,24 +5274,24 @@
       <c r="E114" s="13"/>
       <c r="F114" s="50"/>
       <c r="G114" s="50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H114" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I114" s="50"/>
       <c r="J114" s="50"/>
       <c r="K114" s="50"/>
       <c r="L114" s="50" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="49" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B115" s="52" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="53">
         <v>1401800</v>
@@ -5335,7 +5300,7 @@
         <v>15</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F115" s="50"/>
       <c r="G115" s="50"/>
@@ -5344,15 +5309,15 @@
       <c r="J115" s="50"/>
       <c r="K115" s="50"/>
       <c r="L115" s="50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="49" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B116" s="54" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C116" s="53">
         <v>1530000</v>
@@ -5361,24 +5326,24 @@
         <v>20</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F116" s="50"/>
       <c r="G116" s="50"/>
       <c r="H116" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I116" s="50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J116" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K116" s="50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L116" s="50" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6287,9 +6252,9 @@
     <row r="1020" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A3" r:id="rId1" display=" 46 Federal Rd. Map 131-2-4 (Numerous Permits)" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A4" r:id="rId2" display="24 Hammond Street Map 134-4-2A (Permit 2019)" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A5" r:id="rId3" display="0 Hammond Street: 131 lot 1-3 (Solar)" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="A13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="I13" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="H14" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
